--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.851961374282837</v>
+        <v>3.62965202331543</v>
       </c>
       <c r="E2" t="n">
         <v>0.9993077551606934</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.683156490325928</v>
+        <v>1.720405340194702</v>
       </c>
       <c r="E3" t="n">
         <v>0.9994639056223656</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.851961374282837</v>
+        <v>3.62965202331543</v>
       </c>
       <c r="E2" t="n">
         <v>0.9993077551606934</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.683156490325928</v>
+        <v>1.720405340194702</v>
       </c>
       <c r="E3" t="n">
         <v>0.9994639056223656</v>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.62965202331543</v>
+        <v>2.283513784408569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9993077551606934</v>
+        <v>0.9965440319277402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9995703448167288</v>
+        <v>0.9979411295019519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4084784432314476</v>
+        <v>0.8941772782146106</v>
       </c>
       <c r="H2" t="n">
-        <v>0.252633484183968</v>
+        <v>0.596932118403447</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.720405340194702</v>
+        <v>1.65857720375061</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9994639056223656</v>
+        <v>0.9974903523734235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9996531681509944</v>
+        <v>0.9983181512040402</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3670021430084903</v>
+        <v>0.8081697467762399</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2297141919817243</v>
+        <v>0.5709631694446908</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.62965202331543</v>
+        <v>2.283513784408569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9993077551606934</v>
+        <v>0.9965440319277402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9995703448167288</v>
+        <v>0.9979411295019519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4084784432314476</v>
+        <v>0.8941772782146106</v>
       </c>
       <c r="H2" t="n">
-        <v>0.252633484183968</v>
+        <v>0.596932118403447</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.720405340194702</v>
+        <v>1.65857720375061</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9994639056223656</v>
+        <v>0.9974903523734235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9996531681509944</v>
+        <v>0.9983181512040402</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3670021430084903</v>
+        <v>0.8081697467762399</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2297141919817243</v>
+        <v>0.5709631694446908</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.283513784408569</v>
+        <v>8.396403551101685</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965440319277402</v>
+        <v>0.9536663691202799</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979411295019519</v>
+        <v>0.9612084031105042</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8941772782146106</v>
+        <v>35.04785537719727</v>
       </c>
       <c r="H2" t="n">
-        <v>0.596932118403447</v>
+        <v>21.43936157226562</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.65857720375061</v>
+        <v>10.00616836547852</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974903523734235</v>
+        <v>0.9578738689422608</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9983181512040402</v>
+        <v>0.9612084031105042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8081697467762399</v>
+        <v>35.04785537719727</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5709631694446908</v>
+        <v>21.43936157226562</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20.1418719291687</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.959556657075882</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9602950811386108</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.45803070068359</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22.02004814147949</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.283513784408569</v>
+        <v>8.396403551101685</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965440319277402</v>
+        <v>0.9536663691202799</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979411295019519</v>
+        <v>0.9612084031105042</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8941772782146106</v>
+        <v>35.04785537719727</v>
       </c>
       <c r="H2" t="n">
-        <v>0.596932118403447</v>
+        <v>21.43936157226562</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.65857720375061</v>
+        <v>10.00616836547852</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974903523734235</v>
+        <v>0.9578738689422608</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9983181512040402</v>
+        <v>0.9612084031105042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8081697467762399</v>
+        <v>35.04785537719727</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5709631694446908</v>
+        <v>21.43936157226562</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20.1418719291687</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.959556657075882</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9602950811386108</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.45803070068359</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22.02004814147949</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>8.396403551101685</v>
+        <v>20.94777989387512</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9536663691202799</v>
+        <v>0.9599743843078613</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9612084031105042</v>
+        <v>0.9615880846977234</v>
       </c>
       <c r="G2" t="n">
-        <v>35.04785537719727</v>
+        <v>34.87590026855469</v>
       </c>
       <c r="H2" t="n">
-        <v>21.43936157226562</v>
+        <v>21.44150924682617</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>10.00616836547852</v>
+        <v>24.31270527839661</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9578738689422608</v>
+        <v>0.9605928301811218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9612084031105042</v>
+        <v>0.9602247476577759</v>
       </c>
       <c r="G3" t="n">
-        <v>35.04785537719727</v>
+        <v>35.48942565917969</v>
       </c>
       <c r="H3" t="n">
-        <v>21.43936157226562</v>
+        <v>21.94902038574219</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>20.1418719291687</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.959556657075882</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9602950811386108</v>
-      </c>
-      <c r="G4" t="n">
-        <v>35.45803070068359</v>
-      </c>
-      <c r="H4" t="n">
-        <v>22.02004814147949</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>8.396403551101685</v>
+        <v>20.94777989387512</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9536663691202799</v>
+        <v>0.9599743843078613</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9612084031105042</v>
+        <v>0.9615880846977234</v>
       </c>
       <c r="G2" t="n">
-        <v>35.04785537719727</v>
+        <v>34.87590026855469</v>
       </c>
       <c r="H2" t="n">
-        <v>21.43936157226562</v>
+        <v>21.44150924682617</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>10.00616836547852</v>
+        <v>24.31270527839661</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9578738689422608</v>
+        <v>0.9605928301811218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9612084031105042</v>
+        <v>0.9602247476577759</v>
       </c>
       <c r="G3" t="n">
-        <v>35.04785537719727</v>
+        <v>35.48942565917969</v>
       </c>
       <c r="H3" t="n">
-        <v>21.43936157226562</v>
+        <v>21.94902038574219</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>20.1418719291687</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.959556657075882</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9602950811386108</v>
-      </c>
-      <c r="G4" t="n">
-        <v>35.45803070068359</v>
-      </c>
-      <c r="H4" t="n">
-        <v>22.02004814147949</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.94777989387512</v>
+        <v>3.335872411727905</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9599743843078613</v>
+        <v>0.9965440319277402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9615880846977234</v>
+        <v>0.9979411295019519</v>
       </c>
       <c r="G2" t="n">
-        <v>34.87590026855469</v>
+        <v>0.8941772782146106</v>
       </c>
       <c r="H2" t="n">
-        <v>21.44150924682617</v>
+        <v>0.596932118403447</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>24.31270527839661</v>
+        <v>1.281316995620728</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9605928301811218</v>
+        <v>0.9974903523734235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9602247476577759</v>
+        <v>0.9983181512040402</v>
       </c>
       <c r="G3" t="n">
-        <v>35.48942565917969</v>
+        <v>0.8081697467762399</v>
       </c>
       <c r="H3" t="n">
-        <v>21.94902038574219</v>
+        <v>0.5709631694446908</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.94777989387512</v>
+        <v>3.335872411727905</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9599743843078613</v>
+        <v>0.9965440319277402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9615880846977234</v>
+        <v>0.9979411295019519</v>
       </c>
       <c r="G2" t="n">
-        <v>34.87590026855469</v>
+        <v>0.8941772782146106</v>
       </c>
       <c r="H2" t="n">
-        <v>21.44150924682617</v>
+        <v>0.596932118403447</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>24.31270527839661</v>
+        <v>1.281316995620728</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9605928301811218</v>
+        <v>0.9974903523734235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9602247476577759</v>
+        <v>0.9983181512040402</v>
       </c>
       <c r="G3" t="n">
-        <v>35.48942565917969</v>
+        <v>0.8081697467762399</v>
       </c>
       <c r="H3" t="n">
-        <v>21.94902038574219</v>
+        <v>0.5709631694446908</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.335872411727905</v>
+        <v>3.782261610031128</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965440319277402</v>
+        <v>0.9965485258873344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979411295019519</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8941772782146106</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H2" t="n">
-        <v>0.596932118403447</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.281316995620728</v>
+        <v>1.896116971969604</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974903523734235</v>
+        <v>0.9975184543357718</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9983181512040402</v>
+        <v>0.9983996958198125</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8081697467762399</v>
+        <v>0.7883342302033211</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5709631694446908</v>
+        <v>0.556964816303996</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.335872411727905</v>
+        <v>3.782261610031128</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965440319277402</v>
+        <v>0.9965485258873344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979411295019519</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8941772782146106</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H2" t="n">
-        <v>0.596932118403447</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.281316995620728</v>
+        <v>1.896116971969604</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974903523734235</v>
+        <v>0.9975184543357718</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9983181512040402</v>
+        <v>0.9983996958198125</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8081697467762399</v>
+        <v>0.7883342302033211</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5709631694446908</v>
+        <v>0.556964816303996</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.782261610031128</v>
+        <v>3.592050552368164</v>
       </c>
       <c r="E2" t="n">
         <v>0.9965485258873344</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.896116971969604</v>
+        <v>1.714103698730469</v>
       </c>
       <c r="E3" t="n">
         <v>0.9975184543357718</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.782261610031128</v>
+        <v>3.592050552368164</v>
       </c>
       <c r="E2" t="n">
         <v>0.9965485258873344</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.896116971969604</v>
+        <v>1.714103698730469</v>
       </c>
       <c r="E3" t="n">
         <v>0.9975184543357718</v>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.592050552368164</v>
+        <v>0.8823893070220947</v>
       </c>
       <c r="E2" t="n">
         <v>0.9965485258873344</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.714103698730469</v>
+        <v>0.4276108741760254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9975184543357718</v>
+        <v>0.9974346204770498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9983996958198125</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7883342302033211</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H3" t="n">
-        <v>0.556964816303996</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.592050552368164</v>
+        <v>0.8823893070220947</v>
       </c>
       <c r="E2" t="n">
         <v>0.9965485258873344</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.714103698730469</v>
+        <v>0.4276108741760254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9975184543357718</v>
+        <v>0.9974346204770498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9983996958198125</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7883342302033211</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H3" t="n">
-        <v>0.556964816303996</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8823893070220947</v>
+        <v>350.2020745277405</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965485258873344</v>
+        <v>0.9536898136138916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9616894721984863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883167420157519</v>
+        <v>34.82984924316406</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5851734726150313</v>
+        <v>21.44558906555176</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4276108741760254</v>
+        <v>51.1232898235321</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974346204770498</v>
+        <v>0.9580495715141296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9616894721984863</v>
       </c>
       <c r="G3" t="n">
-        <v>0.883167420157519</v>
+        <v>34.82984924316406</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5851734726150313</v>
+        <v>21.44558906555176</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8823893070220947</v>
+        <v>350.2020745277405</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965485258873344</v>
+        <v>0.9536898136138916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9616894721984863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883167420157519</v>
+        <v>34.82984924316406</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5851734726150313</v>
+        <v>21.44558906555176</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4276108741760254</v>
+        <v>51.1232898235321</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974346204770498</v>
+        <v>0.9580495715141296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9616894721984863</v>
       </c>
       <c r="G3" t="n">
-        <v>0.883167420157519</v>
+        <v>34.82984924316406</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5851734726150313</v>
+        <v>21.44558906555176</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>350.2020745277405</v>
+        <v>1.641574144363403</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9536898136138916</v>
+        <v>0.4397318959236145</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.5523912906646729</v>
       </c>
       <c r="G2" t="n">
-        <v>34.82984924316406</v>
+        <v>0.5887791514396667</v>
       </c>
       <c r="H2" t="n">
-        <v>21.44558906555176</v>
+        <v>0.4128801226615906</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>51.1232898235321</v>
+        <v>1.78523850440979</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9580495715141296</v>
+        <v>0.4812644481658935</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.5523912906646729</v>
       </c>
       <c r="G3" t="n">
-        <v>34.82984924316406</v>
+        <v>0.5887791514396667</v>
       </c>
       <c r="H3" t="n">
-        <v>21.44558906555176</v>
+        <v>0.4128801226615906</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>350.2020745277405</v>
+        <v>1.641574144363403</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9536898136138916</v>
+        <v>0.4397318959236145</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.5523912906646729</v>
       </c>
       <c r="G2" t="n">
-        <v>34.82984924316406</v>
+        <v>0.5887791514396667</v>
       </c>
       <c r="H2" t="n">
-        <v>21.44558906555176</v>
+        <v>0.4128801226615906</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>51.1232898235321</v>
+        <v>1.78523850440979</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9580495715141296</v>
+        <v>0.4812644481658935</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.5523912906646729</v>
       </c>
       <c r="G3" t="n">
-        <v>34.82984924316406</v>
+        <v>0.5887791514396667</v>
       </c>
       <c r="H3" t="n">
-        <v>21.44558906555176</v>
+        <v>0.4128801226615906</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.641574144363403</v>
+        <v>4.459742784500122</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4397318959236145</v>
+        <v>0.4881770610809326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5523912906646729</v>
+        <v>0.5276503562927246</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5887791514396667</v>
+        <v>68.75205993652344</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4128801226615906</v>
+        <v>33.24764251708984</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.78523850440979</v>
+        <v>5.302191972732544</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4812644481658935</v>
+        <v>0.5191580176353454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5523912906646729</v>
+        <v>0.5484093427658081</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5887791514396667</v>
+        <v>67.22431182861328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4128801226615906</v>
+        <v>33.18839645385742</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.641574144363403</v>
+        <v>4.459742784500122</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4397318959236145</v>
+        <v>0.4881770610809326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5523912906646729</v>
+        <v>0.5276503562927246</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5887791514396667</v>
+        <v>68.75205993652344</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4128801226615906</v>
+        <v>33.24764251708984</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.78523850440979</v>
+        <v>5.302191972732544</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4812644481658935</v>
+        <v>0.5191580176353454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5523912906646729</v>
+        <v>0.5484093427658081</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5887791514396667</v>
+        <v>67.22431182861328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4128801226615906</v>
+        <v>33.18839645385742</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.459742784500122</v>
+        <v>3.5017249584198</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4881770610809326</v>
+        <v>0.9965485258873344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5276503562927246</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G2" t="n">
-        <v>68.75205993652344</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H2" t="n">
-        <v>33.24764251708984</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.302191972732544</v>
+        <v>0.4978578090667725</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5191580176353454</v>
+        <v>0.9974346204770498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5484093427658081</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G3" t="n">
-        <v>67.22431182861328</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H3" t="n">
-        <v>33.18839645385742</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7781908512115479</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.459742784500122</v>
+        <v>3.5017249584198</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4881770610809326</v>
+        <v>0.9965485258873344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5276503562927246</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G2" t="n">
-        <v>68.75205993652344</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H2" t="n">
-        <v>33.24764251708984</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.302191972732544</v>
+        <v>0.4978578090667725</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5191580176353454</v>
+        <v>0.9974346204770498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5484093427658081</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G3" t="n">
-        <v>67.22431182861328</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H3" t="n">
-        <v>33.18839645385742</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7781908512115479</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5017249584198</v>
+        <v>3.663124322891235</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965485258873344</v>
+        <v>0.9536898136138916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9616894721984863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883167420157519</v>
+        <v>34.82984924316406</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5851734726150313</v>
+        <v>21.44558906555176</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4978578090667725</v>
+        <v>2.157824516296387</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974346204770498</v>
+        <v>0.9580495715141296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9616894721984863</v>
       </c>
       <c r="G3" t="n">
-        <v>0.883167420157519</v>
+        <v>34.82984924316406</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5851734726150313</v>
+        <v>21.44558906555176</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.7781908512115479</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9977164520836048</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5851734726150313</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5017249584198</v>
+        <v>3.663124322891235</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965485258873344</v>
+        <v>0.9536898136138916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9616894721984863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883167420157519</v>
+        <v>34.82984924316406</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5851734726150313</v>
+        <v>21.44558906555176</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4978578090667725</v>
+        <v>2.157824516296387</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974346204770498</v>
+        <v>0.9580495715141296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9616894721984863</v>
       </c>
       <c r="G3" t="n">
-        <v>0.883167420157519</v>
+        <v>34.82984924316406</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5851734726150313</v>
+        <v>21.44558906555176</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.7781908512115479</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9977164520836048</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5851734726150313</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.663124322891235</v>
+        <v>5.649735450744629</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9536898136138916</v>
+        <v>0.9997890436781206</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.9998042027416953</v>
       </c>
       <c r="G2" t="n">
-        <v>34.82984924316406</v>
+        <v>0.134329942329803</v>
       </c>
       <c r="H2" t="n">
-        <v>21.44558906555176</v>
+        <v>0.05678066230454196</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.157824516296387</v>
+        <v>5.960345983505249</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9580495715141296</v>
+        <v>0.9998118365660742</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.9998042027416953</v>
       </c>
       <c r="G3" t="n">
-        <v>34.82984924316406</v>
+        <v>0.134329942329803</v>
       </c>
       <c r="H3" t="n">
-        <v>21.44558906555176</v>
+        <v>0.05678066230454196</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.663124322891235</v>
+        <v>5.649735450744629</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9536898136138916</v>
+        <v>0.9997890436781206</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.9998042027416953</v>
       </c>
       <c r="G2" t="n">
-        <v>34.82984924316406</v>
+        <v>0.134329942329803</v>
       </c>
       <c r="H2" t="n">
-        <v>21.44558906555176</v>
+        <v>0.05678066230454196</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.157824516296387</v>
+        <v>5.960345983505249</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9580495715141296</v>
+        <v>0.9998118365660742</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.9998042027416953</v>
       </c>
       <c r="G3" t="n">
-        <v>34.82984924316406</v>
+        <v>0.134329942329803</v>
       </c>
       <c r="H3" t="n">
-        <v>21.44558906555176</v>
+        <v>0.05678066230454196</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.649735450744629</v>
+        <v>5.446849346160889</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9997890436781206</v>
+        <v>0.4881770610809326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998042027416953</v>
+        <v>0.5276503562927246</v>
       </c>
       <c r="G2" t="n">
-        <v>0.134329942329803</v>
+        <v>68.75205993652344</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05678066230454196</v>
+        <v>33.24764251708984</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.960345983505249</v>
+        <v>5.661454677581787</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9998118365660742</v>
+        <v>0.5191580176353454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9998042027416953</v>
+        <v>0.5484093427658081</v>
       </c>
       <c r="G3" t="n">
-        <v>0.134329942329803</v>
+        <v>67.22431182861328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05678066230454196</v>
+        <v>33.18839645385742</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.649735450744629</v>
+        <v>5.446849346160889</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9997890436781206</v>
+        <v>0.4881770610809326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998042027416953</v>
+        <v>0.5276503562927246</v>
       </c>
       <c r="G2" t="n">
-        <v>0.134329942329803</v>
+        <v>68.75205993652344</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05678066230454196</v>
+        <v>33.24764251708984</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.960345983505249</v>
+        <v>5.661454677581787</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9998118365660742</v>
+        <v>0.5191580176353454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9998042027416953</v>
+        <v>0.5484093427658081</v>
       </c>
       <c r="G3" t="n">
-        <v>0.134329942329803</v>
+        <v>67.22431182861328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05678066230454196</v>
+        <v>33.18839645385742</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.446849346160889</v>
+        <v>15.64453220367432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4881770610809326</v>
+        <v>0.9152503745433745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5276503562927246</v>
+        <v>0.9309440281122273</v>
       </c>
       <c r="G2" t="n">
-        <v>68.75205993652344</v>
+        <v>8.915659227845845</v>
       </c>
       <c r="H2" t="n">
-        <v>33.24764251708984</v>
+        <v>5.212121269458375</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.661454677581787</v>
+        <v>19.70489597320557</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5191580176353454</v>
+        <v>0.9202444657974951</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5484093427658081</v>
+        <v>0.9309440281122273</v>
       </c>
       <c r="G3" t="n">
-        <v>67.22431182861328</v>
+        <v>8.915659227845845</v>
       </c>
       <c r="H3" t="n">
-        <v>33.18839645385742</v>
+        <v>5.212121269458375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.446849346160889</v>
+        <v>15.64453220367432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4881770610809326</v>
+        <v>0.9152503745433745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5276503562927246</v>
+        <v>0.9309440281122273</v>
       </c>
       <c r="G2" t="n">
-        <v>68.75205993652344</v>
+        <v>8.915659227845845</v>
       </c>
       <c r="H2" t="n">
-        <v>33.24764251708984</v>
+        <v>5.212121269458375</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.661454677581787</v>
+        <v>19.70489597320557</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5191580176353454</v>
+        <v>0.9202444657974951</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5484093427658081</v>
+        <v>0.9309440281122273</v>
       </c>
       <c r="G3" t="n">
-        <v>67.22431182861328</v>
+        <v>8.915659227845845</v>
       </c>
       <c r="H3" t="n">
-        <v>33.18839645385742</v>
+        <v>5.212121269458375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>15.64453220367432</v>
+        <v>6.800420999526978</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9152503745433745</v>
+        <v>0.4397318959236145</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9309440281122273</v>
+        <v>0.5523912906646729</v>
       </c>
       <c r="G2" t="n">
-        <v>8.915659227845845</v>
+        <v>0.5887791514396667</v>
       </c>
       <c r="H2" t="n">
-        <v>5.212121269458375</v>
+        <v>0.4128801226615906</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>19.70489597320557</v>
+        <v>7.363279819488525</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9202444657974951</v>
+        <v>0.4839082956314087</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9309440281122273</v>
+        <v>0.5292840003967285</v>
       </c>
       <c r="G3" t="n">
-        <v>8.915659227845845</v>
+        <v>0.6037854552268982</v>
       </c>
       <c r="H3" t="n">
-        <v>5.212121269458375</v>
+        <v>0.4324872493743896</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>15.64453220367432</v>
+        <v>6.800420999526978</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9152503745433745</v>
+        <v>0.4397318959236145</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9309440281122273</v>
+        <v>0.5523912906646729</v>
       </c>
       <c r="G2" t="n">
-        <v>8.915659227845845</v>
+        <v>0.5887791514396667</v>
       </c>
       <c r="H2" t="n">
-        <v>5.212121269458375</v>
+        <v>0.4128801226615906</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>19.70489597320557</v>
+        <v>7.363279819488525</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9202444657974951</v>
+        <v>0.4839082956314087</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9309440281122273</v>
+        <v>0.5292840003967285</v>
       </c>
       <c r="G3" t="n">
-        <v>8.915659227845845</v>
+        <v>0.6037854552268982</v>
       </c>
       <c r="H3" t="n">
-        <v>5.212121269458375</v>
+        <v>0.4324872493743896</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.800420999526978</v>
+        <v>3.052937507629395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4397318959236145</v>
+        <v>0.9965485258873344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5523912906646729</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5887791514396667</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4128801226615906</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.363279819488525</v>
+        <v>0.4700894355773926</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4839082956314087</v>
+        <v>0.9974346204770498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5292840003967285</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6037854552268982</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4324872493743896</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7690708637237549</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.800420999526978</v>
+        <v>3.052937507629395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4397318959236145</v>
+        <v>0.9965485258873344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5523912906646729</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5887791514396667</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4128801226615906</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.363279819488525</v>
+        <v>0.4700894355773926</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4839082956314087</v>
+        <v>0.9974346204770498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5292840003967285</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6037854552268982</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4324872493743896</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7690708637237549</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.052937507629395</v>
+        <v>3.060005187988281</v>
       </c>
       <c r="E2" t="n">
         <v>0.9965485258873344</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4700894355773926</v>
+        <v>0.4157588481903076</v>
       </c>
       <c r="E3" t="n">
         <v>0.9974346204770498</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7690708637237549</v>
+        <v>0.6667060852050781</v>
       </c>
       <c r="E4" t="n">
         <v>0.9977164520836048</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.052937507629395</v>
+        <v>3.060005187988281</v>
       </c>
       <c r="E2" t="n">
         <v>0.9965485258873344</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4700894355773926</v>
+        <v>0.4157588481903076</v>
       </c>
       <c r="E3" t="n">
         <v>0.9974346204770498</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7690708637237549</v>
+        <v>0.6667060852050781</v>
       </c>
       <c r="E4" t="n">
         <v>0.9977164520836048</v>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>3.060005187988281</v>
+        <v>5.200452327728271</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965485258873344</v>
+        <v>0.939555150270462</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9362788796424866</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883167420157519</v>
+        <v>33.66668319702148</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5851734726150313</v>
+        <v>20.24748420715332</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4157588481903076</v>
+        <v>5.034294128417969</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974346204770498</v>
+        <v>0.9401066422462463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.935413122177124</v>
       </c>
       <c r="G3" t="n">
-        <v>0.883167420157519</v>
+        <v>33.89462280273438</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5851734726150313</v>
+        <v>20.38737678527832</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.6667060852050781</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9977164520836048</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5851734726150313</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>3.060005187988281</v>
+        <v>5.200452327728271</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965485258873344</v>
+        <v>0.939555150270462</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9362788796424866</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883167420157519</v>
+        <v>33.66668319702148</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5851734726150313</v>
+        <v>20.24748420715332</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4157588481903076</v>
+        <v>5.034294128417969</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974346204770498</v>
+        <v>0.9401066422462463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.935413122177124</v>
       </c>
       <c r="G3" t="n">
-        <v>0.883167420157519</v>
+        <v>33.89462280273438</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5851734726150313</v>
+        <v>20.38737678527832</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.6667060852050781</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9977164520836048</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5851734726150313</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,59 +488,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.200452327728271</v>
+        <v>4.529591083526611</v>
       </c>
       <c r="E2" t="n">
-        <v>0.939555150270462</v>
+        <v>0.9338110486666361</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9362788796424866</v>
+        <v>0.935413122177124</v>
       </c>
       <c r="G2" t="n">
-        <v>33.66668319702148</v>
+        <v>33.89462280273438</v>
       </c>
       <c r="H2" t="n">
-        <v>20.24748420715332</v>
+        <v>20.38737678527832</v>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5.034294128417969</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9401066422462463</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.935413122177124</v>
-      </c>
-      <c r="G3" t="n">
-        <v>33.89462280273438</v>
-      </c>
-      <c r="H3" t="n">
-        <v>20.38737678527832</v>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
@@ -557,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,59 +584,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.200452327728271</v>
+        <v>4.529591083526611</v>
       </c>
       <c r="E2" t="n">
-        <v>0.939555150270462</v>
+        <v>0.9338110486666361</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9362788796424866</v>
+        <v>0.935413122177124</v>
       </c>
       <c r="G2" t="n">
-        <v>33.66668319702148</v>
+        <v>33.89462280273438</v>
       </c>
       <c r="H2" t="n">
-        <v>20.24748420715332</v>
+        <v>20.38737678527832</v>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5.034294128417969</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9401066422462463</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.935413122177124</v>
-      </c>
-      <c r="G3" t="n">
-        <v>33.89462280273438</v>
-      </c>
-      <c r="H3" t="n">
-        <v>20.38737678527832</v>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,93 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.529591083526611</v>
+        <v>3.02683162689209</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9338110486666361</v>
+        <v>0.9965485258873344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.935413122177124</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G2" t="n">
-        <v>33.89462280273438</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H2" t="n">
-        <v>20.38737678527832</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3923439979553223</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9974346204770498</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7825050354003906</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -522,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,23 +657,93 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.529591083526611</v>
+        <v>3.02683162689209</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9338110486666361</v>
+        <v>0.9965485258873344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.935413122177124</v>
+        <v>0.9979915184339837</v>
       </c>
       <c r="G2" t="n">
-        <v>33.89462280273438</v>
+        <v>0.883167420157519</v>
       </c>
       <c r="H2" t="n">
-        <v>20.38737678527832</v>
+        <v>0.5851734726150313</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3923439979553223</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9974346204770498</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7825050354003906</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.02683162689209</v>
+        <v>7.062656402587891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965485258873344</v>
+        <v>0.99982357862805</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9998209317977906</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883167420157519</v>
+        <v>0.1268976817616241</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5851734726150313</v>
+        <v>0.05364276771399302</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3923439979553223</v>
+        <v>7.810389280319214</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974346204770498</v>
+        <v>0.9998247893839546</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9998267509010639</v>
       </c>
       <c r="G3" t="n">
-        <v>0.883167420157519</v>
+        <v>0.1248187829825181</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5851734726150313</v>
+        <v>0.05288277202897447</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.7825050354003906</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9977164520836048</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5851734726150313</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.02683162689209</v>
+        <v>7.062656402587891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9965485258873344</v>
+        <v>0.99982357862805</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9998209317977906</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883167420157519</v>
+        <v>0.1268976817616241</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5851734726150313</v>
+        <v>0.05364276771399302</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3923439979553223</v>
+        <v>7.810389280319214</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9974346204770498</v>
+        <v>0.9998247893839546</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9979915184339837</v>
+        <v>0.9998267509010639</v>
       </c>
       <c r="G3" t="n">
-        <v>0.883167420157519</v>
+        <v>0.1248187829825181</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5851734726150313</v>
+        <v>0.05288277202897447</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.7825050354003906</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9977164520836048</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5851734726150313</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.062656402587891</v>
+        <v>6.135040760040283</v>
       </c>
       <c r="E2" t="n">
         <v>0.99982357862805</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.810389280319214</v>
+        <v>7.205111026763916</v>
       </c>
       <c r="E3" t="n">
         <v>0.9998247893839546</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.062656402587891</v>
+        <v>6.135040760040283</v>
       </c>
       <c r="E2" t="n">
         <v>0.99982357862805</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.810389280319214</v>
+        <v>7.205111026763916</v>
       </c>
       <c r="E3" t="n">
         <v>0.9998247893839546</v>
